--- a/artfynd/A 19534-2025 artfynd.xlsx
+++ b/artfynd/A 19534-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1228,6 +1228,228 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>124825373</v>
+      </c>
+      <c r="B7" t="n">
+        <v>78905</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>967</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Varglav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Letharia vulpina</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Hue</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Trängslet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>429341</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6807517</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering. Liten tuss på stubbe</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>124825372</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92293</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Trängslet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>429109</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6807561</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 19534-2025 artfynd.xlsx
+++ b/artfynd/A 19534-2025 artfynd.xlsx
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124825373</v>
+        <v>124825372</v>
       </c>
       <c r="B7" t="n">
-        <v>78905</v>
+        <v>92293</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,25 +1242,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>967</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>429341</v>
+        <v>429109</v>
       </c>
       <c r="R7" t="n">
-        <v>6807517</v>
+        <v>6807561</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering. Liten tuss på stubbe</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124825372</v>
+        <v>124825373</v>
       </c>
       <c r="B8" t="n">
-        <v>92293</v>
+        <v>78905</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,25 +1353,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>967</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>429109</v>
+        <v>429341</v>
       </c>
       <c r="R8" t="n">
-        <v>6807561</v>
+        <v>6807517</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering. Liten tuss på stubbe</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 19534-2025 artfynd.xlsx
+++ b/artfynd/A 19534-2025 artfynd.xlsx
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124825372</v>
+        <v>124825373</v>
       </c>
       <c r="B7" t="n">
-        <v>92293</v>
+        <v>78905</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,25 +1242,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>967</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>429109</v>
+        <v>429341</v>
       </c>
       <c r="R7" t="n">
-        <v>6807561</v>
+        <v>6807517</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering. Liten tuss på stubbe</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124825373</v>
+        <v>124825372</v>
       </c>
       <c r="B8" t="n">
-        <v>78905</v>
+        <v>92293</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,25 +1353,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>967</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>429341</v>
+        <v>429109</v>
       </c>
       <c r="R8" t="n">
-        <v>6807517</v>
+        <v>6807561</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering. Liten tuss på stubbe</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 19534-2025 artfynd.xlsx
+++ b/artfynd/A 19534-2025 artfynd.xlsx
@@ -1233,7 +1233,7 @@
         <v>124825372</v>
       </c>
       <c r="B7" t="n">
-        <v>92293</v>
+        <v>92448</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>124825373</v>
       </c>
       <c r="B8" t="n">
-        <v>78905</v>
+        <v>79042</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 19534-2025 artfynd.xlsx
+++ b/artfynd/A 19534-2025 artfynd.xlsx
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124825372</v>
+        <v>124825373</v>
       </c>
       <c r="B7" t="n">
-        <v>92448</v>
+        <v>79042</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,25 +1242,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>967</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>429109</v>
+        <v>429341</v>
       </c>
       <c r="R7" t="n">
-        <v>6807561</v>
+        <v>6807517</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering. Liten tuss på stubbe</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124825373</v>
+        <v>124825372</v>
       </c>
       <c r="B8" t="n">
-        <v>79042</v>
+        <v>92448</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,25 +1353,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>967</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>429341</v>
+        <v>429109</v>
       </c>
       <c r="R8" t="n">
-        <v>6807517</v>
+        <v>6807561</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering. Liten tuss på stubbe</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
         </is>
       </c>
       <c r="AD8" t="b">
